--- a/offers/seasonal/عروض انوجين.xlsx
+++ b/offers/seasonal/عروض انوجين.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\9\عروض اليوم الوطني\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\9\عروض اليوم الوطني\Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C635EFE-B424-44D1-A6ED-3C438119209A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5993E56-DDE0-4A3F-90C6-992F79191B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -40,112 +40,55 @@
     <t>تاريخ بداية العرض</t>
   </si>
   <si>
-    <t>نوع العرض</t>
-  </si>
-  <si>
-    <t>كمية</t>
-  </si>
-  <si>
     <t>1+1</t>
   </si>
   <si>
-    <t>00043316</t>
-  </si>
-  <si>
     <t>INNOGEN MAXGEN 30 SACHETS</t>
   </si>
   <si>
-    <t>00044972</t>
-  </si>
-  <si>
     <t>INNOGEN VISCOFLU 20 SACHETS </t>
   </si>
   <si>
-    <t>00026292</t>
-  </si>
-  <si>
     <t>INNOGEN IRON LIPO IRON 30GUM</t>
   </si>
   <si>
-    <t>00044962</t>
-  </si>
-  <si>
     <t>INNOGEN VITAFILL D3 DROPS 10ML </t>
   </si>
   <si>
-    <t>00026293</t>
-  </si>
-  <si>
     <t>INNOGEN MULTIVITAMIN LIPO MAX 30GUM</t>
   </si>
   <si>
-    <t>00043303</t>
-  </si>
-  <si>
     <t>INNOGEN ACYST 300MG 30 CAP </t>
   </si>
   <si>
-    <t>00043314</t>
-  </si>
-  <si>
     <t>INNOGEN LIPOCOBAL VIT-B12 DROPS </t>
   </si>
   <si>
-    <t>00043318</t>
-  </si>
-  <si>
     <t>INNOGEN VENOLEN IDROGEL 100ML</t>
   </si>
   <si>
-    <t>00043315</t>
-  </si>
-  <si>
     <t>INNOGEN LIPO D3 VITAMI D3 </t>
   </si>
   <si>
-    <t>00044967</t>
-  </si>
-  <si>
     <t>INNOGEN VITAFILL B12 30ML DROPS </t>
   </si>
   <si>
-    <t>00044963</t>
-  </si>
-  <si>
     <t>INNOGEN DUOVITA DROPS </t>
   </si>
   <si>
-    <t>00026291</t>
-  </si>
-  <si>
     <t>INNOGEN VITAMIN C LIPO C GUM ORANGE 30GUM</t>
   </si>
   <si>
-    <t>00043304</t>
-  </si>
-  <si>
     <t>INNOGE FERI PRO 8MICRO VIALS </t>
   </si>
   <si>
-    <t>00043317</t>
-  </si>
-  <si>
     <t>INNOGEN REEMA CRANBERRY 30 GUM</t>
   </si>
   <si>
-    <t>00044965</t>
-  </si>
-  <si>
     <t>INNOGEN LIPO CURCUMIN 250ML </t>
   </si>
   <si>
-    <t>00044964</t>
-  </si>
-  <si>
     <t>INNOGEN ENDURO 25ML 30VIALS </t>
-  </si>
-  <si>
-    <t>00044966</t>
   </si>
   <si>
     <t>INNOGEN RESTORE 10ML 30VIAL </t>
@@ -213,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -232,6 +175,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -602,22 +546,20 @@
       <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
+      <c r="A2" s="8">
+        <v>43316</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3">
         <v>458.85</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2" s="5">
         <v>46305</v>
@@ -625,22 +567,19 @@
       <c r="F2" s="5">
         <v>46275</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
+      <c r="A3" s="8">
+        <v>44972</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3">
         <v>65.55</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" s="5">
         <v>46305</v>
@@ -648,22 +587,19 @@
       <c r="F3" s="5">
         <v>46275</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
+      <c r="A4" s="8">
+        <v>26292</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3">
         <v>117</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" s="5">
         <v>46305</v>
@@ -671,22 +607,19 @@
       <c r="F4" s="5">
         <v>46275</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
+      <c r="A5" s="8">
+        <v>44962</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3">
         <v>47</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E5" s="5">
         <v>46305</v>
@@ -694,22 +627,19 @@
       <c r="F5" s="5">
         <v>46275</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
+      <c r="A6" s="8">
+        <v>26293</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3">
         <v>103.99</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="5">
         <v>46305</v>
@@ -717,22 +647,19 @@
       <c r="F6" s="5">
         <v>46275</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
+      <c r="A7" s="8">
+        <v>43303</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3">
         <v>85.1</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" s="5">
         <v>46305</v>
@@ -740,22 +667,19 @@
       <c r="F7" s="5">
         <v>46275</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
+      <c r="A8" s="8">
+        <v>43314</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3">
         <v>113.85</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" s="5">
         <v>46305</v>
@@ -763,22 +687,19 @@
       <c r="F8" s="5">
         <v>46275</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
+      <c r="A9" s="8">
+        <v>43318</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3">
         <v>75.900000000000006</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" s="5">
         <v>46305</v>
@@ -786,22 +707,19 @@
       <c r="F9" s="5">
         <v>46275</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
+      <c r="A10" s="8">
+        <v>43315</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3">
         <v>103.99</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10" s="5">
         <v>46305</v>
@@ -809,22 +727,19 @@
       <c r="F10" s="5">
         <v>46275</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
+      <c r="A11" s="8">
+        <v>44967</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3">
         <v>89</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E11" s="5">
         <v>46305</v>
@@ -832,22 +747,19 @@
       <c r="F11" s="5">
         <v>46275</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>29</v>
+      <c r="A12" s="8">
+        <v>44963</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3">
         <v>123.05</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5">
         <v>46305</v>
@@ -855,22 +767,19 @@
       <c r="F12" s="5">
         <v>46275</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>31</v>
+      <c r="A13" s="8">
+        <v>26291</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3">
         <v>111</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E13" s="5">
         <v>46305</v>
@@ -878,22 +787,19 @@
       <c r="F13" s="5">
         <v>46275</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
+      <c r="A14" s="8">
+        <v>43304</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3">
         <v>92</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E14" s="5">
         <v>46305</v>
@@ -901,22 +807,19 @@
       <c r="F14" s="5">
         <v>46275</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>35</v>
+      <c r="A15" s="8">
+        <v>43317</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3">
         <v>156</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" s="5">
         <v>46305</v>
@@ -924,22 +827,19 @@
       <c r="F15" s="5">
         <v>46275</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>37</v>
+      <c r="A16" s="8">
+        <v>44965</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C16" s="3">
         <v>217.35</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="5">
         <v>46305</v>
@@ -947,22 +847,19 @@
       <c r="F16" s="5">
         <v>46275</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>39</v>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>44964</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3">
         <v>299.98</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" s="5">
         <v>46305</v>
@@ -970,22 +867,19 @@
       <c r="F17" s="5">
         <v>46275</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>41</v>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <v>44966</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3">
         <v>310.5</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18" s="5">
         <v>46305</v>
@@ -993,63 +887,60 @@
       <c r="F18" s="5">
         <v>46275</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
@@ -1817,7 +1708,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>